--- a/fixtures/files/intelliplan_timmar_MBAB_2026-09_andrad.xlsx
+++ b/fixtures/files/intelliplan_timmar_MBAB_2026-09_andrad.xlsx
@@ -477,7 +477,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F5" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G5" t="str">
         <v>1/9 2026</v>
@@ -506,7 +506,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F6" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G6" s="1">
         <v>46267</v>
@@ -535,7 +535,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F7" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G7" t="str">
         <v>5/9 2026</v>
@@ -564,7 +564,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F8" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G8" s="1">
         <v>46277</v>
@@ -593,7 +593,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F9" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G9" s="1">
         <v>46281</v>
@@ -622,7 +622,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F10" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G10" s="1">
         <v>46282</v>
@@ -651,7 +651,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F11" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G11" s="1">
         <v>46286</v>
@@ -680,7 +680,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F12" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G12" t="str">
         <v>24/9 2026</v>
@@ -709,7 +709,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F13" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G13" s="1">
         <v>46291</v>
@@ -738,7 +738,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="F14" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="G14" t="str">
         <v>2026-09-28</v>
@@ -767,7 +767,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F15" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G15" s="1">
         <v>46267</v>
@@ -796,7 +796,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F16" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G16" s="1">
         <v>46268</v>
@@ -825,7 +825,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F17" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G17" t="str">
         <v>6/9 2026</v>
@@ -854,7 +854,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F18" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G18" s="1">
         <v>46272</v>
@@ -883,7 +883,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F19" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G19" t="str">
         <v>13/9 2026</v>
@@ -912,7 +912,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F20" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G20" t="str">
         <v>14/9 2026</v>
@@ -941,7 +941,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F21" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G21" s="1">
         <v>46281</v>
@@ -970,7 +970,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F22" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G22" s="1">
         <v>46289</v>
@@ -999,7 +999,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F23" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G23" s="1">
         <v>46290</v>
@@ -1028,7 +1028,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="F24" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="G24" t="str">
         <v>2026-09-26</v>
@@ -1057,7 +1057,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F25" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G25" s="1">
         <v>46267</v>
@@ -1086,7 +1086,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F26" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G26" s="1">
         <v>46268</v>
@@ -1115,7 +1115,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F27" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G27" t="str">
         <v>4/9 2026</v>
@@ -1144,7 +1144,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F28" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G28" t="str">
         <v>6/9 2026</v>
@@ -1173,7 +1173,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F29" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G29" s="1">
         <v>46278</v>
@@ -1202,7 +1202,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F30" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G30" t="str">
         <v>15/9 2026</v>
@@ -1231,7 +1231,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F31" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G31" s="1">
         <v>46281</v>
@@ -1260,7 +1260,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F32" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G32" t="str">
         <v>21/9 2026</v>
@@ -1289,7 +1289,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F33" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G33" s="1">
         <v>46287</v>
@@ -1318,7 +1318,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F34" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G34" t="str">
         <v>23/9 2026</v>
@@ -1347,7 +1347,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F35" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G35" s="1">
         <v>46291</v>
@@ -1376,7 +1376,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="F36" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="G36" s="1">
         <v>46295</v>
@@ -1405,7 +1405,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F37" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G37" s="1">
         <v>46268</v>
@@ -1434,7 +1434,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F38" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G38" t="str">
         <v>4/9 2026</v>
@@ -1463,7 +1463,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F39" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G39" s="1">
         <v>46270</v>
@@ -1492,7 +1492,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F40" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G40" s="1">
         <v>46275</v>
@@ -1521,7 +1521,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F41" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G41" t="str">
         <v>11/9 2026</v>
@@ -1550,7 +1550,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F42" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G42" s="1">
         <v>46277</v>
@@ -1579,7 +1579,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F43" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G43" s="1">
         <v>46284</v>
@@ -1608,7 +1608,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F44" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G44" s="1">
         <v>46286</v>
@@ -1637,7 +1637,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F45" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G45" s="1">
         <v>46287</v>
@@ -1666,7 +1666,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F46" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G46" t="str">
         <v>23/9 2026</v>
@@ -1695,7 +1695,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F47" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G47" s="1">
         <v>46291</v>
@@ -1724,7 +1724,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F48" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G48" t="str">
         <v>28/9 2026</v>
@@ -1753,7 +1753,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="F49" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="G49" s="1">
         <v>46295</v>
@@ -1782,7 +1782,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F50" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G50" s="1">
         <v>46267</v>
@@ -1811,7 +1811,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F51" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G51" s="1">
         <v>46268</v>
@@ -1840,7 +1840,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F52" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G52" s="1">
         <v>46270</v>
@@ -1869,7 +1869,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F53" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G53" s="1">
         <v>46271</v>
@@ -1898,7 +1898,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F54" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G54" s="1">
         <v>46273</v>
@@ -1927,7 +1927,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F55" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G55" s="1">
         <v>46276</v>
@@ -1956,7 +1956,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F56" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G56" s="1">
         <v>46278</v>
@@ -1985,7 +1985,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F57" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G57" s="1">
         <v>46280</v>
@@ -2014,7 +2014,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F58" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G58" s="1">
         <v>46286</v>
@@ -2043,7 +2043,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="F59" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="G59" t="str">
         <v>24/9 2026</v>
@@ -2072,7 +2072,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="F60" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="G60" s="1">
         <v>46272</v>
@@ -2101,7 +2101,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="F61" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="G61" s="1">
         <v>46276</v>
@@ -2130,7 +2130,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="F62" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="G62" s="1">
         <v>46267</v>
@@ -2159,7 +2159,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="F63" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="G63" s="1">
         <v>46269</v>
@@ -2188,7 +2188,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="F64" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="G64" s="1">
         <v>46278</v>
@@ -2217,7 +2217,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="F65" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="G65" s="1">
         <v>46279</v>
@@ -2246,7 +2246,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="F66" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="G66" s="1">
         <v>46284</v>
@@ -2275,7 +2275,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="F67" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="G67" s="1">
         <v>46288</v>
@@ -2304,7 +2304,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="F68" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="G68" t="str">
         <v>28/9 2026</v>
@@ -2333,7 +2333,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="F69" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="G69" s="1">
         <v>46294</v>
@@ -2362,7 +2362,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="F71" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="G71" t="str">
         <v>2/9 2026</v>
@@ -2391,7 +2391,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="F72" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="G72" s="1">
         <v>46269</v>
@@ -2420,7 +2420,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="F73" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="G73" s="1">
         <v>46270</v>
@@ -2449,7 +2449,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="F74" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="G74" s="1">
         <v>46274</v>
@@ -2478,7 +2478,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="F75" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="G75" s="1">
         <v>46275</v>
@@ -2507,7 +2507,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="F76" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="G76" t="str">
         <v>2026-09-13</v>
@@ -2536,7 +2536,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="F77" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="G77" s="1">
         <v>46279</v>
@@ -2565,7 +2565,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="F78" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="G78" t="str">
         <v>16/9 2026</v>
@@ -2594,7 +2594,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="F79" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="G79" t="str">
         <v>2026-09-17</v>
@@ -2623,7 +2623,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="F80" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="G80" t="str">
         <v>2026-09-05</v>
@@ -2652,7 +2652,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="F81" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="G81" t="str">
         <v>8/9 2026</v>
@@ -2681,7 +2681,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="F82" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="G82" s="1">
         <v>46279</v>
@@ -2710,7 +2710,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="F83" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="G83" t="str">
         <v>21/9 2026</v>
@@ -2739,7 +2739,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="F84" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="G84" t="str">
         <v>2026-09-23</v>
@@ -2768,7 +2768,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="F85" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="G85" s="1">
         <v>46289</v>
@@ -2797,7 +2797,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="F86" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="G86" s="1">
         <v>46295</v>
@@ -2826,7 +2826,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="F87" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="G87" t="str">
         <v>2026-09-09</v>
@@ -2855,7 +2855,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="F88" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="G88" t="str">
         <v>2026-09-15</v>
@@ -2884,7 +2884,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="F89" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="G89" s="1">
         <v>46287</v>
@@ -2913,7 +2913,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="F90" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="G90" s="1">
         <v>46292</v>
@@ -2942,7 +2942,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F91" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G91" t="str">
         <v>2/9 2026</v>
@@ -2971,7 +2971,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F92" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G92" t="str">
         <v>3/9 2026</v>
@@ -3000,7 +3000,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F93" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G93" s="1">
         <v>46269</v>
@@ -3029,7 +3029,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F94" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G94" s="1">
         <v>46270</v>
@@ -3058,7 +3058,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F95" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G95" s="1">
         <v>46273</v>
@@ -3087,7 +3087,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F96" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G96" t="str">
         <v>2026-09-09</v>
@@ -3116,7 +3116,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F97" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G97" s="1">
         <v>46278</v>
@@ -3145,7 +3145,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F98" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G98" s="1">
         <v>46279</v>
@@ -3174,7 +3174,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F99" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G99" s="1">
         <v>46281</v>
@@ -3203,7 +3203,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F100" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G100" s="1">
         <v>46283</v>
@@ -3232,7 +3232,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F101" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G101" s="1">
         <v>46286</v>
@@ -3261,7 +3261,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="F102" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="G102" t="str">
         <v>2026-09-28</v>
@@ -3290,7 +3290,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F103" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G103" s="1">
         <v>46266</v>
@@ -3319,7 +3319,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F104" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G104" s="1">
         <v>46280</v>
@@ -3348,7 +3348,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F105" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G105" t="str">
         <v>16/9 2026</v>
@@ -3377,7 +3377,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F106" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G106" s="1">
         <v>46288</v>
@@ -3406,7 +3406,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F107" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G107" s="1">
         <v>46289</v>
@@ -3435,7 +3435,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F108" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G108" s="1">
         <v>46294</v>
@@ -3464,7 +3464,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F109" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G109" s="1">
         <v>46295</v>
@@ -3493,7 +3493,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="F110" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="G110" s="1">
         <v>46273</v>
@@ -3522,7 +3522,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="F111" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="G111" s="1">
         <v>46274</v>
@@ -3551,7 +3551,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="F112" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="G112" t="str">
         <v>16/9 2026</v>
@@ -3580,7 +3580,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="F113" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="G113" t="str">
         <v>2026-09-24</v>
@@ -3609,7 +3609,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="F114" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="G114" s="1">
         <v>46290</v>
@@ -3638,7 +3638,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="F115" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="G115" t="str">
         <v>28/9 2026</v>
@@ -3667,7 +3667,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="F116" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="G116" t="str">
         <v>30/9 2026</v>
@@ -3719,7 +3719,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F119" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G119" s="1">
         <v>46267</v>
@@ -3748,7 +3748,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F120" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G120" t="str">
         <v>2026-09-05</v>
@@ -3777,7 +3777,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F121" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G121" t="str">
         <v>9/9 2026</v>
@@ -3806,7 +3806,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F122" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G122" s="1">
         <v>46291</v>
@@ -3835,7 +3835,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F123" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G123" s="1">
         <v>46292</v>
@@ -3864,7 +3864,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F124" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G124" t="str">
         <v>28/9 2026</v>
@@ -3893,7 +3893,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F125" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G125" s="1">
         <v>46267</v>
@@ -3922,7 +3922,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F126" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G126" s="1">
         <v>46271</v>
@@ -3951,7 +3951,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F127" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G127" s="1">
         <v>46273</v>
@@ -3980,7 +3980,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F128" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G128" s="1">
         <v>46279</v>
@@ -4009,7 +4009,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F129" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G129" s="1">
         <v>46281</v>
@@ -4038,7 +4038,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F130" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G130" t="str">
         <v>17/9 2026</v>
@@ -4067,7 +4067,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F131" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G131" t="str">
         <v>2026-09-21</v>
@@ -4096,7 +4096,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F132" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G132" s="1">
         <v>46293</v>
@@ -4125,7 +4125,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F133" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G133" s="1">
         <v>46266</v>
@@ -4154,7 +4154,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F134" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G134" s="1">
         <v>46267</v>
@@ -4183,7 +4183,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F135" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G135" t="str">
         <v>3/9 2026</v>
@@ -4212,7 +4212,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F136" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G136" s="1">
         <v>46270</v>
@@ -4241,7 +4241,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F137" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G137" s="1">
         <v>46271</v>
@@ -4270,7 +4270,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F138" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G138" s="1">
         <v>46272</v>
@@ -4299,7 +4299,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F139" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G139" s="1">
         <v>46274</v>
@@ -4328,7 +4328,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F140" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G140" s="1">
         <v>46275</v>
@@ -4357,7 +4357,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F141" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G141" s="1">
         <v>46278</v>
@@ -4386,7 +4386,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F142" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G142" s="1">
         <v>46279</v>
@@ -4415,7 +4415,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F143" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G143" s="1">
         <v>46280</v>
@@ -4444,7 +4444,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F144" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G144" s="1">
         <v>46281</v>
@@ -4473,7 +4473,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="F145" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="G145" s="1">
         <v>46282</v>
@@ -4502,7 +4502,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="F146" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="G146" s="1">
         <v>46267</v>
@@ -4531,7 +4531,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="F147" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="G147" s="1">
         <v>46268</v>
@@ -4560,7 +4560,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="F148" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="G148" t="str">
         <v>3/9 2026</v>
@@ -4589,7 +4589,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="F149" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="G149" t="str">
         <v>6/9 2026</v>
@@ -4618,7 +4618,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="F150" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="G150" s="1">
         <v>46274</v>
@@ -4647,7 +4647,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="F151" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="G151" t="str">
         <v>13/9 2026</v>
@@ -4676,7 +4676,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="F152" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="G152" t="str">
         <v>17/9 2026</v>
@@ -4705,7 +4705,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="F153" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="G153" t="str">
         <v>20/9 2026</v>
@@ -4734,7 +4734,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="F154" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="G154" s="1">
         <v>46288</v>
@@ -4763,7 +4763,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="F155" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="G155" s="1">
         <v>46270</v>
@@ -4792,7 +4792,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="F156" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="G156" t="str">
         <v>21/9 2026</v>
@@ -4844,7 +4844,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="F158" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="G158" t="str">
         <v>2026-09-03</v>
@@ -4873,7 +4873,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="F159" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="G159" s="1">
         <v>46271</v>
@@ -4902,7 +4902,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="F160" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="G160" s="1">
         <v>46272</v>
@@ -4931,7 +4931,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="F161" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="G161" t="str">
         <v>20/9 2026</v>
@@ -4960,7 +4960,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F162" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G162" t="str">
         <v>2026-09-04</v>
@@ -4989,7 +4989,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F163" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G163" t="str">
         <v>2026-09-08</v>
@@ -5018,7 +5018,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F164" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G164" s="1">
         <v>46278</v>
@@ -5047,7 +5047,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F165" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G165" s="1">
         <v>46284</v>
@@ -5076,7 +5076,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F166" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G166" s="1">
         <v>46286</v>
@@ -5105,7 +5105,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F167" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G167" s="1">
         <v>46287</v>
@@ -5134,7 +5134,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F168" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G168" t="str">
         <v>23/9 2026</v>
@@ -5163,7 +5163,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F169" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G169" s="1">
         <v>46293</v>
@@ -5192,7 +5192,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F170" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G170" s="1">
         <v>46294</v>
@@ -5221,7 +5221,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F171" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G171" s="1">
         <v>46272</v>
@@ -5250,7 +5250,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F172" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G172" t="str">
         <v>8/9 2026</v>
@@ -5279,7 +5279,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F173" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G173" s="1">
         <v>46274</v>
@@ -5308,7 +5308,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F174" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G174" s="1">
         <v>46276</v>
@@ -5337,7 +5337,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F175" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G175" t="str">
         <v>12/9 2026</v>
@@ -5366,7 +5366,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F176" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G176" s="1">
         <v>46278</v>
@@ -5395,7 +5395,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F177" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G177" s="1">
         <v>46279</v>
@@ -5424,7 +5424,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F178" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G178" s="1">
         <v>46281</v>
@@ -5453,7 +5453,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F179" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G179" t="str">
         <v>17/9 2026</v>
@@ -5482,7 +5482,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F180" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G180" t="str">
         <v>19/9 2026</v>
@@ -5511,7 +5511,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F181" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G181" t="str">
         <v>2026-09-27</v>
@@ -5540,7 +5540,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="F182" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="G182" s="1">
         <v>46293</v>
@@ -5569,7 +5569,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="F183" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="G183" s="1">
         <v>46266</v>
@@ -5598,7 +5598,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="F184" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="G184" s="1">
         <v>46269</v>
@@ -5627,7 +5627,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="F185" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="G185" s="1">
         <v>46282</v>
@@ -5656,7 +5656,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="F186" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="G186" t="str">
         <v>2026-09-19</v>
@@ -5685,7 +5685,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="F187" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="G187" t="str">
         <v>26/9 2026</v>
@@ -5714,7 +5714,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="F189" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="G189" s="1">
         <v>46273</v>
@@ -5743,7 +5743,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="F190" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="G190" s="1">
         <v>46274</v>
@@ -5772,7 +5772,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="F191" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="G191" s="1">
         <v>46279</v>
@@ -5801,7 +5801,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="F192" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="G192" s="1">
         <v>46284</v>
@@ -5830,7 +5830,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="F193" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="G193" s="1">
         <v>46285</v>
@@ -5859,7 +5859,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="F194" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="G194" s="1">
         <v>46290</v>
@@ -5888,7 +5888,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="F195" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="G195" s="1">
         <v>46291</v>
@@ -5917,7 +5917,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="F196" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="G196" s="1">
         <v>46294</v>
@@ -5946,7 +5946,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="F197" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="G197" s="1">
         <v>46267</v>
@@ -5975,7 +5975,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="F198" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="G198" t="str">
         <v>8/9 2026</v>
@@ -6004,7 +6004,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="F199" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="G199" s="1">
         <v>46276</v>
@@ -6033,7 +6033,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="F200" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="G200" t="str">
         <v>12/9 2026</v>
@@ -6062,7 +6062,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="F201" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="G201" s="1">
         <v>46279</v>
@@ -6091,7 +6091,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="F202" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="G202" s="1">
         <v>46282</v>
@@ -6120,7 +6120,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="F203" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="G203" s="1">
         <v>46287</v>
@@ -6149,7 +6149,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="F204" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="G204" s="1">
         <v>46292</v>
@@ -6178,7 +6178,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="F205" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="G205" s="1">
         <v>46293</v>
@@ -6207,7 +6207,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="F206" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="G206" s="1">
         <v>46277</v>
@@ -6236,7 +6236,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="F207" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="G207" s="1">
         <v>46279</v>
@@ -6265,7 +6265,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="F208" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="G208" t="str">
         <v>2026-09-17</v>
@@ -6294,7 +6294,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="F209" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="G209" s="1">
         <v>46284</v>
@@ -6323,7 +6323,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="F210" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="G210" s="1">
         <v>46290</v>
@@ -6352,7 +6352,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="F211" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="G211" s="1">
         <v>46291</v>
@@ -6381,7 +6381,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F212" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G212" t="str">
         <v>2/9 2026</v>
@@ -6410,7 +6410,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F213" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G213" s="1">
         <v>46271</v>
@@ -6439,7 +6439,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F214" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G214" t="str">
         <v>10/9 2026</v>
@@ -6468,7 +6468,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F215" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G215" t="str">
         <v>12/9 2026</v>
@@ -6497,7 +6497,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F216" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G216" t="str">
         <v>13/9 2026</v>
@@ -6526,7 +6526,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F217" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G217" s="1">
         <v>46281</v>
@@ -6555,7 +6555,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F218" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G218" t="str">
         <v>18/9 2026</v>
@@ -6584,7 +6584,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F219" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G219" s="1">
         <v>46286</v>
@@ -6613,7 +6613,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F220" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G220" t="str">
         <v>23/9 2026</v>
@@ -6642,7 +6642,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F221" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G221" s="1">
         <v>46291</v>
@@ -6671,7 +6671,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F222" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G222" s="1">
         <v>46292</v>
@@ -6700,7 +6700,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F223" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G223" s="1">
         <v>46293</v>
@@ -6729,7 +6729,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="F224" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="G224" s="1">
         <v>46294</v>
@@ -6758,7 +6758,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F225" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G225" t="str">
         <v>21/9 2026</v>
@@ -6787,7 +6787,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F226" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G226" s="1">
         <v>46287</v>
@@ -6816,7 +6816,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F227" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G227" s="1">
         <v>46288</v>
@@ -6845,7 +6845,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F228" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G228" t="str">
         <v>2026-09-24</v>
@@ -6874,7 +6874,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F229" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G229" s="1">
         <v>46290</v>
@@ -6903,7 +6903,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F230" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G230" s="1">
         <v>46291</v>
@@ -6932,7 +6932,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F231" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G231" t="str">
         <v>27/9 2026</v>
@@ -6961,7 +6961,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F232" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G232" s="1">
         <v>46293</v>
@@ -6990,7 +6990,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F233" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G233" s="1">
         <v>46294</v>
@@ -7019,7 +7019,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="F234" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="G234" t="str">
         <v>30/9 2026</v>
@@ -7048,7 +7048,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="F235" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="G235" s="1">
         <v>46271</v>
@@ -7077,7 +7077,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="F236" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="G236" s="1">
         <v>46272</v>
@@ -7106,7 +7106,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="F237" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="G237" t="str">
         <v>11/9 2026</v>
@@ -7135,7 +7135,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="F238" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="G238" s="1">
         <v>46277</v>
@@ -7164,7 +7164,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="F239" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="G239" t="str">
         <v>2026-09-16</v>
@@ -7193,7 +7193,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="F240" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="G240" s="1">
         <v>46287</v>
@@ -7222,7 +7222,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="F241" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="G241" t="str">
         <v>2026-09-23</v>
@@ -7251,7 +7251,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="F242" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="G242" t="str">
         <v>26/9 2026</v>
@@ -7280,7 +7280,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="F243" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="G243" s="1">
         <v>46293</v>
@@ -7309,7 +7309,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F244" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G244" s="1">
         <v>46273</v>
@@ -7338,7 +7338,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F245" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G245" s="1">
         <v>46275</v>
@@ -7367,7 +7367,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F246" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G246" s="1">
         <v>46276</v>
@@ -7396,7 +7396,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F247" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G247" s="1">
         <v>46277</v>
@@ -7425,7 +7425,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F248" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G248" s="1">
         <v>46279</v>
@@ -7454,7 +7454,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F249" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G249" t="str">
         <v>2026-09-15</v>
@@ -7483,7 +7483,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F250" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G250" s="1">
         <v>46282</v>
@@ -7512,7 +7512,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F251" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G251" t="str">
         <v>18/9 2026</v>
@@ -7541,7 +7541,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F252" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G252" s="1">
         <v>46284</v>
@@ -7570,7 +7570,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F253" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G253" s="1">
         <v>46285</v>
@@ -7599,7 +7599,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F254" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G254" s="1">
         <v>46287</v>
@@ -7628,7 +7628,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F255" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G255" s="1">
         <v>46290</v>
@@ -7657,7 +7657,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F256" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G256" t="str">
         <v>29/9 2026</v>
@@ -7686,7 +7686,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="F257" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="G257" s="1">
         <v>46295</v>
@@ -7738,7 +7738,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="F259" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="G259" s="1">
         <v>46276</v>
@@ -7767,7 +7767,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="F260" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="G260" s="1">
         <v>46278</v>
@@ -7796,7 +7796,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="F261" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="G261" s="1">
         <v>46279</v>
@@ -7825,7 +7825,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="F262" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="G262" s="1">
         <v>46288</v>
@@ -7854,7 +7854,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F263" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G263" s="1">
         <v>46275</v>
@@ -7883,7 +7883,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F264" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G264" t="str">
         <v>12/9 2026</v>
@@ -7912,7 +7912,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F265" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G265" s="1">
         <v>46280</v>
@@ -7941,7 +7941,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F266" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G266" s="1">
         <v>46282</v>
@@ -7970,7 +7970,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F267" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G267" s="1">
         <v>46283</v>
@@ -7999,7 +7999,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F268" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G268" t="str">
         <v>2026-09-19</v>
@@ -8028,7 +8028,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F269" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G269" s="1">
         <v>46285</v>
@@ -8057,7 +8057,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F270" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G270" t="str">
         <v>21/9 2026</v>
@@ -8086,7 +8086,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F271" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G271" s="1">
         <v>46287</v>
@@ -8115,7 +8115,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F272" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G272" s="1">
         <v>46288</v>
@@ -8144,7 +8144,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F273" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G273" s="1">
         <v>46291</v>
@@ -8173,7 +8173,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F274" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G274" s="1">
         <v>46293</v>
@@ -8202,7 +8202,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="F275" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="G275" s="1">
         <v>46295</v>
@@ -8231,7 +8231,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="F276" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="G276" s="1">
         <v>46266</v>
@@ -8260,7 +8260,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="F277" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="G277" s="1">
         <v>46267</v>
@@ -8289,7 +8289,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="F278" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="G278" t="str">
         <v>26/9 2026</v>
@@ -8318,7 +8318,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="F279" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="G279" s="1">
         <v>46293</v>
@@ -8526,7 +8526,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="F289" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="G289" t="str">
         <v>2026-09-14</v>
@@ -8555,7 +8555,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="F290" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="G290" s="1">
         <v>46293</v>
@@ -8584,7 +8584,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="F291" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="G291" s="1">
         <v>46295</v>
@@ -8613,7 +8613,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F292" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G292" t="str">
         <v>2026-09-01</v>
@@ -8642,7 +8642,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="F293" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="G293" s="1">
         <v>46283</v>
@@ -8671,7 +8671,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F294" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G294" s="1">
         <v>46271</v>
@@ -8700,7 +8700,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F295" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G295" s="1">
         <v>46279</v>
@@ -8729,7 +8729,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="F296" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="G296" s="1">
         <v>46289</v>
@@ -8758,7 +8758,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F297" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G297" s="1">
         <v>46266</v>
@@ -8787,7 +8787,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F298" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G298" t="str">
         <v>2/9 2026</v>
@@ -8816,7 +8816,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F299" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G299" t="str">
         <v>7/9 2026</v>
@@ -8845,7 +8845,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F300" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G300" t="str">
         <v>2026-09-08</v>
@@ -8874,7 +8874,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F301" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G301" t="str">
         <v>12/9 2026</v>
@@ -8903,7 +8903,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F302" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G302" t="str">
         <v>2026-09-14</v>
@@ -8932,7 +8932,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F303" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G303" s="1">
         <v>46280</v>
@@ -8961,7 +8961,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F304" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G304" s="1">
         <v>46281</v>
@@ -8990,7 +8990,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F305" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G305" t="str">
         <v>20/9 2026</v>
@@ -9019,7 +9019,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F306" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G306" s="1">
         <v>46286</v>
@@ -9048,7 +9048,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F307" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G307" t="str">
         <v>22/9 2026</v>
@@ -9077,7 +9077,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F308" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G308" t="str">
         <v>26/9 2026</v>
@@ -9106,7 +9106,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="F309" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="G309" s="1">
         <v>46293</v>
@@ -9135,7 +9135,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="F310" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="G310" t="str">
         <v>25/9 2026</v>
@@ -9164,7 +9164,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="F311" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="G311" t="str">
         <v>26/9 2026</v>
@@ -9193,7 +9193,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="F312" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="G312" t="str">
         <v>2026-09-27</v>
@@ -9222,7 +9222,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="F313" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="G313" t="str">
         <v>28/9 2026</v>
@@ -9251,7 +9251,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="F314" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="G314" s="1">
         <v>46294</v>
@@ -9280,7 +9280,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="F315" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="G315" s="1">
         <v>46295</v>
@@ -9309,7 +9309,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F316" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G316" s="1">
         <v>46269</v>
@@ -9338,7 +9338,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F317" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G317" s="1">
         <v>46270</v>
@@ -9367,7 +9367,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F318" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G318" s="1">
         <v>46280</v>
@@ -9396,7 +9396,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F319" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G319" t="str">
         <v>2026-09-17</v>
@@ -9425,7 +9425,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F320" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G320" s="1">
         <v>46284</v>
@@ -9454,7 +9454,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F321" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G321" s="1">
         <v>46285</v>
@@ -9483,7 +9483,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F322" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G322" s="1">
         <v>46289</v>
@@ -9512,7 +9512,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F323" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G323" s="1">
         <v>46290</v>
@@ -9541,7 +9541,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F324" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G324" t="str">
         <v>28/9 2026</v>
@@ -9570,7 +9570,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="F325" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="G325" s="1">
         <v>46294</v>
@@ -9622,7 +9622,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="F328" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="G328" s="1">
         <v>46272</v>
@@ -9651,7 +9651,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="F329" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="G329" s="1">
         <v>46289</v>
@@ -9680,7 +9680,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="F330" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="G330" s="1">
         <v>46270</v>
@@ -9709,7 +9709,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="F331" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="G331" s="1">
         <v>46274</v>
@@ -9738,7 +9738,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="F332" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="G332" t="str">
         <v>11/9 2026</v>
@@ -9767,7 +9767,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="F333" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="G333" s="1">
         <v>46277</v>
@@ -9796,7 +9796,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="F334" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="G334" s="1">
         <v>46279</v>
@@ -9825,7 +9825,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="F335" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="G335" s="1">
         <v>46295</v>
@@ -9854,7 +9854,7 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="F336" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="G336" s="1">
         <v>46272</v>
@@ -9883,7 +9883,7 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="F337" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="G337" s="1">
         <v>46275</v>
@@ -9912,7 +9912,7 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="F338" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="G338" s="1">
         <v>46281</v>
@@ -9941,7 +9941,7 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="F339" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="G339" s="1">
         <v>46288</v>
@@ -9970,7 +9970,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F340" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G340" s="1">
         <v>46267</v>
@@ -9999,7 +9999,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F341" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G341" t="str">
         <v>3/9 2026</v>
@@ -10028,7 +10028,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F342" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G342" s="1">
         <v>46273</v>
@@ -10057,7 +10057,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F343" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G343" t="str">
         <v>13/9 2026</v>
@@ -10086,7 +10086,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F344" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G344" t="str">
         <v>14/9 2026</v>
@@ -10115,7 +10115,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F345" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G345" s="1">
         <v>46282</v>
@@ -10144,7 +10144,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F346" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G346" t="str">
         <v>2026-09-18</v>
@@ -10173,7 +10173,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F347" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G347" s="1">
         <v>46288</v>
@@ -10202,7 +10202,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F348" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G348" s="1">
         <v>46289</v>
@@ -10231,7 +10231,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="F349" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="G349" t="str">
         <v>26/9 2026</v>
@@ -10352,7 +10352,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F354" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G354" s="1">
         <v>46270</v>
@@ -10381,7 +10381,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F355" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G355" s="1">
         <v>46272</v>
@@ -10410,7 +10410,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F356" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G356" t="str">
         <v>2026-09-08</v>
@@ -10439,7 +10439,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F357" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G357" s="1">
         <v>46277</v>
@@ -10468,7 +10468,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F358" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G358" s="1">
         <v>46278</v>
@@ -10497,7 +10497,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F359" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G359" s="1">
         <v>46279</v>
@@ -10526,7 +10526,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F360" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G360" s="1">
         <v>46280</v>
@@ -10555,7 +10555,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F361" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G361" s="1">
         <v>46282</v>
@@ -10584,7 +10584,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F362" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G362" s="1">
         <v>46284</v>
@@ -10613,7 +10613,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F363" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G363" s="1">
         <v>46285</v>
@@ -10642,7 +10642,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F364" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G364" s="1">
         <v>46287</v>
@@ -10671,7 +10671,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F365" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G365" s="1">
         <v>46290</v>
@@ -10700,7 +10700,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F366" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G366" s="1">
         <v>46292</v>
@@ -10729,7 +10729,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="F367" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="G367" t="str">
         <v>28/9 2026</v>
@@ -10758,7 +10758,7 @@
         <v>Omar Ahmed</v>
       </c>
       <c r="F369" t="str">
-        <v>19811109-0448</v>
+        <v>19811109-9803</v>
       </c>
       <c r="G369" s="1">
         <v>46266</v>
@@ -10787,7 +10787,7 @@
         <v>Omar Ahmed</v>
       </c>
       <c r="F370" t="str">
-        <v>19811109-0448</v>
+        <v>19811109-9803</v>
       </c>
       <c r="G370" t="str">
         <v>2026-09-15</v>
@@ -10816,7 +10816,7 @@
         <v>Omar Ahmed</v>
       </c>
       <c r="F371" t="str">
-        <v>19811109-0448</v>
+        <v>19811109-9803</v>
       </c>
       <c r="G371" t="str">
         <v>16/9 2026</v>
@@ -10845,7 +10845,7 @@
         <v>Omar Ahmed</v>
       </c>
       <c r="F372" t="str">
-        <v>19811109-0448</v>
+        <v>19811109-9803</v>
       </c>
       <c r="G372" s="1">
         <v>46285</v>
@@ -10874,7 +10874,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F373" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G373" s="1">
         <v>46266</v>
@@ -10903,7 +10903,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F374" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G374" s="1">
         <v>46267</v>
@@ -10932,7 +10932,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F375" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G375" s="1">
         <v>46273</v>
@@ -10961,7 +10961,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F376" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G376" t="str">
         <v>12/9 2026</v>
@@ -10990,7 +10990,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F377" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G377" t="str">
         <v>13/9 2026</v>
@@ -11019,7 +11019,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F378" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G378" s="1">
         <v>46280</v>
@@ -11048,7 +11048,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F379" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G379" s="1">
         <v>46281</v>
@@ -11077,7 +11077,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F380" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G380" t="str">
         <v>18/9 2026</v>
@@ -11106,7 +11106,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F381" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G381" s="1">
         <v>46284</v>
@@ -11135,7 +11135,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F382" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G382" s="1">
         <v>46288</v>
@@ -11164,7 +11164,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F383" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G383" s="1">
         <v>46293</v>
@@ -11193,7 +11193,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="F384" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="G384" s="1">
         <v>46295</v>
@@ -11222,7 +11222,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F385" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G385" s="1">
         <v>46269</v>
@@ -11251,7 +11251,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F386" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G386" s="1">
         <v>46271</v>
@@ -11280,7 +11280,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F387" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G387" t="str">
         <v>8/9 2026</v>
@@ -11309,7 +11309,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F388" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G388" s="1">
         <v>46276</v>
@@ -11338,7 +11338,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F389" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G389" s="1">
         <v>46284</v>
@@ -11367,7 +11367,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F390" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G390" s="1">
         <v>46288</v>
@@ -11396,7 +11396,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="F391" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="G391" t="str">
         <v>2026-09-24</v>
@@ -11425,7 +11425,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="F392" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="G392" s="1">
         <v>46266</v>
@@ -11454,7 +11454,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="F393" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="G393" t="str">
         <v>2026-09-01</v>
@@ -11483,7 +11483,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="F394" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="G394" s="1">
         <v>46275</v>
@@ -11512,7 +11512,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="F395" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="G395" s="1">
         <v>46278</v>
@@ -11541,7 +11541,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="F396" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="G396" s="1">
         <v>46288</v>
@@ -11570,7 +11570,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="F397" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="G397" s="1">
         <v>46291</v>
@@ -11599,7 +11599,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="F398" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="G398" s="1">
         <v>46293</v>
@@ -11628,7 +11628,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="F399" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="G399" s="1">
         <v>46294</v>
@@ -11657,7 +11657,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F400" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G400" t="str">
         <v>2026-09-02</v>
@@ -11686,7 +11686,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F401" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G401" s="1">
         <v>46274</v>
@@ -11715,7 +11715,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F402" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G402" s="1">
         <v>46277</v>
@@ -11744,7 +11744,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F403" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G403" t="str">
         <v>13/9 2026</v>
@@ -11773,7 +11773,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F404" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G404" s="1">
         <v>46284</v>
@@ -11802,7 +11802,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="F405" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="G405" t="str">
         <v>27/9 2026</v>
@@ -11831,7 +11831,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="F406" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="G406" s="1">
         <v>46267</v>
@@ -11860,7 +11860,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="F407" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="G407" s="1">
         <v>46268</v>
@@ -11889,7 +11889,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="F408" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="G408" t="str">
         <v>7/9 2026</v>
@@ -11918,7 +11918,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="F409" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="G409" s="1">
         <v>46273</v>
@@ -11947,7 +11947,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="F410" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="G410" s="1">
         <v>46274</v>
@@ -11976,7 +11976,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="F411" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="G411" s="1">
         <v>46275</v>
@@ -12005,7 +12005,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="F412" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="G412" t="str">
         <v>2026-09-11</v>
@@ -12034,7 +12034,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="F413" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="G413" s="1">
         <v>46278</v>
@@ -12063,7 +12063,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="F414" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="G414" s="1">
         <v>46266</v>
@@ -12092,7 +12092,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="F415" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="G415" s="1">
         <v>46269</v>
@@ -12121,7 +12121,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="F416" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="G416" t="str">
         <v>2026-09-07</v>
@@ -12150,7 +12150,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="F417" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="G417" s="1">
         <v>46275</v>
@@ -12179,7 +12179,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="F418" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="G418" s="1">
         <v>46278</v>
@@ -12208,7 +12208,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="F419" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="G419" t="str">
         <v>2026-09-24</v>
@@ -12237,7 +12237,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="F420" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="G420" t="str">
         <v>30/9 2026</v>
@@ -12266,7 +12266,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F422" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G422" s="1">
         <v>46268</v>
@@ -12295,7 +12295,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F423" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G423" t="str">
         <v>4/9 2026</v>
@@ -12324,7 +12324,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F424" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G424" s="1">
         <v>46270</v>
@@ -12353,7 +12353,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F425" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G425" s="1">
         <v>46276</v>
@@ -12382,7 +12382,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F426" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G426" s="1">
         <v>46279</v>
@@ -12411,7 +12411,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F427" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G427" s="1">
         <v>46282</v>
@@ -12440,7 +12440,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F428" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G428" s="1">
         <v>46285</v>
@@ -12469,7 +12469,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F429" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G429" s="1">
         <v>46289</v>
@@ -12498,7 +12498,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F430" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G430" t="str">
         <v>26/9 2026</v>
@@ -12527,7 +12527,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F431" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G431" t="str">
         <v>27/9 2026</v>
@@ -12556,7 +12556,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="F432" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="G432" s="1">
         <v>46295</v>
